--- a/TachPP_BL_ChiTiet_KetQua.xlsx
+++ b/TachPP_BL_ChiTiet_KetQua.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Times New Roman"/>
       <family val="2"/>
@@ -61,6 +61,19 @@
     <font>
       <name val="Times New Roman"/>
       <i val="1"/>
+      <color rgb="001B5E20"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="001B5E20"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <i val="1"/>
       <color rgb="007B3F00"/>
       <sz val="11"/>
     </font>
@@ -72,7 +85,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +102,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
@@ -263,7 +281,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -410,6 +428,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3742,7 +3781,7 @@
       </c>
       <c r="Q45" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
@@ -6477,262 +6516,262 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="47" t="inlineStr">
+      <c r="A88" s="54" t="inlineStr">
         <is>
           <t>3.53.65.160.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B88" s="47" t="inlineStr">
+      <c r="B88" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24KV 250-500/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C88" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D88" s="48" t="n">
+      <c r="C88" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D88" s="55" t="n">
         <v>3</v>
       </c>
-      <c r="E88" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F88" s="49" t="n">
+      <c r="E88" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F88" s="56" t="n">
         <v>46105</v>
       </c>
-      <c r="G88" s="48" t="inlineStr">
+      <c r="G88" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0016</t>
         </is>
       </c>
-      <c r="H88" s="48" t="n"/>
-      <c r="I88" s="47" t="inlineStr">
+      <c r="H88" s="55" t="n"/>
+      <c r="I88" s="54" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI TT SCL 2026</t>
         </is>
       </c>
-      <c r="J88" s="50" t="n">
+      <c r="J88" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="K88" s="50" t="n">
+      <c r="K88" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L88" s="50" t="n">
+      <c r="L88" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="M88" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" s="52" t="inlineStr">
+      <c r="M88" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q88" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q88" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="47" t="inlineStr">
+      <c r="A89" s="54" t="inlineStr">
         <is>
           <t>3.53.65.145.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B89" s="47" t="inlineStr">
+      <c r="B89" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 20-40/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C89" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D89" s="48" t="n">
+      <c r="C89" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D89" s="55" t="n">
         <v>3</v>
       </c>
-      <c r="E89" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F89" s="49" t="n">
+      <c r="E89" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F89" s="56" t="n">
         <v>46105</v>
       </c>
-      <c r="G89" s="48" t="inlineStr">
+      <c r="G89" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0016</t>
         </is>
       </c>
-      <c r="H89" s="48" t="n"/>
-      <c r="I89" s="47" t="inlineStr">
+      <c r="H89" s="55" t="n"/>
+      <c r="I89" s="54" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI TT SCL 2026</t>
         </is>
       </c>
-      <c r="J89" s="50" t="n">
+      <c r="J89" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="K89" s="50" t="n">
+      <c r="K89" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L89" s="50" t="n">
+      <c r="L89" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="M89" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" s="52" t="inlineStr">
+      <c r="M89" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q89" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q89" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="47" t="inlineStr">
+      <c r="A90" s="54" t="inlineStr">
         <is>
           <t>3.53.65.147.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B90" s="47" t="inlineStr">
+      <c r="B90" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24KV 30-60/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C90" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D90" s="48" t="n">
+      <c r="C90" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D90" s="55" t="n">
         <v>3</v>
       </c>
-      <c r="E90" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F90" s="49" t="n">
+      <c r="E90" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F90" s="56" t="n">
         <v>46105</v>
       </c>
-      <c r="G90" s="48" t="inlineStr">
+      <c r="G90" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0016</t>
         </is>
       </c>
-      <c r="H90" s="48" t="n"/>
-      <c r="I90" s="47" t="inlineStr">
+      <c r="H90" s="55" t="n"/>
+      <c r="I90" s="54" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI TT SCL 2026</t>
         </is>
       </c>
-      <c r="J90" s="50" t="n">
+      <c r="J90" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="K90" s="50" t="n">
+      <c r="K90" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L90" s="50" t="n">
+      <c r="L90" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="M90" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" s="52" t="inlineStr">
+      <c r="M90" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q90" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q90" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="47" t="inlineStr">
+      <c r="A91" s="54" t="inlineStr">
         <is>
           <t>3.53.65.025.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B91" s="47" t="inlineStr">
+      <c r="B91" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 25-50/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C91" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D91" s="48" t="n">
+      <c r="C91" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D91" s="55" t="n">
         <v>3</v>
       </c>
-      <c r="E91" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F91" s="49" t="n">
+      <c r="E91" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F91" s="56" t="n">
         <v>46105</v>
       </c>
-      <c r="G91" s="48" t="inlineStr">
+      <c r="G91" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0016</t>
         </is>
       </c>
-      <c r="H91" s="48" t="n"/>
-      <c r="I91" s="47" t="inlineStr">
+      <c r="H91" s="55" t="n"/>
+      <c r="I91" s="54" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI TT SCL 2026</t>
         </is>
       </c>
-      <c r="J91" s="50" t="n">
+      <c r="J91" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="K91" s="50" t="n">
+      <c r="K91" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L91" s="50" t="n">
+      <c r="L91" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="M91" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" s="52" t="inlineStr">
+      <c r="M91" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q91" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q91" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
@@ -7192,67 +7231,67 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="47" t="inlineStr">
+      <c r="A99" s="54" t="inlineStr">
         <is>
           <t>3.53.65.145.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B99" s="47" t="inlineStr">
+      <c r="B99" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 20-40/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C99" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D99" s="48" t="n">
+      <c r="C99" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D99" s="55" t="n">
         <v>3</v>
       </c>
-      <c r="E99" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F99" s="49" t="n">
+      <c r="E99" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F99" s="56" t="n">
         <v>46107</v>
       </c>
-      <c r="G99" s="48" t="inlineStr">
+      <c r="G99" s="55" t="inlineStr">
         <is>
           <t>01.VH4.11.0039</t>
         </is>
       </c>
-      <c r="H99" s="48" t="n"/>
-      <c r="I99" s="47" t="inlineStr">
+      <c r="H99" s="55" t="n"/>
+      <c r="I99" s="54" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI TT thay SCL</t>
         </is>
       </c>
-      <c r="J99" s="50" t="n">
+      <c r="J99" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="K99" s="50" t="n">
+      <c r="K99" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L99" s="50" t="n">
+      <c r="L99" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="M99" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" s="52" t="inlineStr">
+      <c r="M99" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q99" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q99" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
@@ -9272,457 +9311,457 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="47" t="inlineStr">
+      <c r="A131" s="54" t="inlineStr">
         <is>
           <t>3.53.65.025.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B131" s="47" t="inlineStr">
+      <c r="B131" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 25-50/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C131" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D131" s="48" t="n">
+      <c r="C131" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D131" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="E131" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F131" s="49" t="n">
+      <c r="E131" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F131" s="56" t="n">
         <v>46122</v>
       </c>
-      <c r="G131" s="48" t="inlineStr">
+      <c r="G131" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H131" s="48" t="n"/>
-      <c r="I131" s="47" t="inlineStr">
+      <c r="H131" s="55" t="n"/>
+      <c r="I131" s="54" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J131" s="50" t="n">
+      <c r="J131" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="K131" s="50" t="n">
+      <c r="K131" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L131" s="50" t="n">
+      <c r="L131" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="M131" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N131" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O131" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" s="52" t="inlineStr">
+      <c r="M131" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q131" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q131" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="47" t="inlineStr">
+      <c r="A132" s="54" t="inlineStr">
         <is>
           <t>3.53.65.160.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B132" s="47" t="inlineStr">
+      <c r="B132" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24KV 250-500/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C132" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D132" s="48" t="n">
+      <c r="C132" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D132" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="E132" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F132" s="49" t="n">
+      <c r="E132" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F132" s="56" t="n">
         <v>46122</v>
       </c>
-      <c r="G132" s="48" t="inlineStr">
+      <c r="G132" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H132" s="48" t="n"/>
-      <c r="I132" s="47" t="inlineStr">
+      <c r="H132" s="55" t="n"/>
+      <c r="I132" s="54" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J132" s="50" t="n">
+      <c r="J132" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="K132" s="50" t="n">
+      <c r="K132" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L132" s="50" t="n">
+      <c r="L132" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="M132" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N132" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O132" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P132" s="52" t="inlineStr">
+      <c r="M132" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q132" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q132" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="47" t="inlineStr">
+      <c r="A133" s="54" t="inlineStr">
         <is>
           <t>3.53.65.145.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B133" s="47" t="inlineStr">
+      <c r="B133" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 20-40/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C133" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D133" s="48" t="n">
+      <c r="C133" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D133" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="E133" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F133" s="49" t="n">
+      <c r="E133" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F133" s="56" t="n">
         <v>46122</v>
       </c>
-      <c r="G133" s="48" t="inlineStr">
+      <c r="G133" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H133" s="48" t="n"/>
-      <c r="I133" s="47" t="inlineStr">
+      <c r="H133" s="55" t="n"/>
+      <c r="I133" s="54" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J133" s="50" t="n">
+      <c r="J133" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="K133" s="50" t="n">
+      <c r="K133" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L133" s="50" t="n">
+      <c r="L133" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="M133" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N133" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O133" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" s="52" t="inlineStr">
+      <c r="M133" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q133" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q133" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="47" t="inlineStr">
+      <c r="A134" s="54" t="inlineStr">
         <is>
           <t>3.53.65.013.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B134" s="47" t="inlineStr">
+      <c r="B134" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 10-20/5A</t>
         </is>
       </c>
-      <c r="C134" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D134" s="48" t="n">
+      <c r="C134" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D134" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="E134" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F134" s="49" t="n">
+      <c r="E134" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F134" s="56" t="n">
         <v>46122</v>
       </c>
-      <c r="G134" s="48" t="inlineStr">
+      <c r="G134" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H134" s="48" t="n"/>
-      <c r="I134" s="47" t="inlineStr">
+      <c r="H134" s="55" t="n"/>
+      <c r="I134" s="54" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J134" s="50" t="n">
+      <c r="J134" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="K134" s="50" t="n">
+      <c r="K134" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L134" s="50" t="n">
+      <c r="L134" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="M134" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N134" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O134" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" s="52" t="inlineStr">
+      <c r="M134" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q134" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q134" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="47" t="inlineStr">
+      <c r="A135" s="54" t="inlineStr">
         <is>
           <t>3.53.65.015.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B135" s="47" t="inlineStr">
+      <c r="B135" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 15-30/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C135" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D135" s="48" t="n">
+      <c r="C135" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D135" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="E135" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F135" s="49" t="n">
+      <c r="E135" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F135" s="56" t="n">
         <v>46122</v>
       </c>
-      <c r="G135" s="48" t="inlineStr">
+      <c r="G135" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H135" s="48" t="n"/>
-      <c r="I135" s="47" t="inlineStr">
+      <c r="H135" s="55" t="n"/>
+      <c r="I135" s="54" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J135" s="50" t="n">
+      <c r="J135" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="K135" s="50" t="n">
+      <c r="K135" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L135" s="50" t="n">
+      <c r="L135" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="M135" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N135" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O135" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" s="52" t="inlineStr">
+      <c r="M135" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q135" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q135" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="47" t="inlineStr">
+      <c r="A136" s="54" t="inlineStr">
         <is>
           <t>3.53.65.148.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B136" s="47" t="inlineStr">
+      <c r="B136" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 50-100/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C136" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D136" s="48" t="n">
+      <c r="C136" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D136" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="E136" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F136" s="49" t="n">
+      <c r="E136" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F136" s="56" t="n">
         <v>46122</v>
       </c>
-      <c r="G136" s="48" t="inlineStr">
+      <c r="G136" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H136" s="48" t="n"/>
-      <c r="I136" s="47" t="inlineStr">
+      <c r="H136" s="55" t="n"/>
+      <c r="I136" s="54" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J136" s="50" t="n">
+      <c r="J136" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="K136" s="50" t="n">
+      <c r="K136" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L136" s="50" t="n">
+      <c r="L136" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="M136" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N136" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O136" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P136" s="52" t="inlineStr">
+      <c r="M136" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q136" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q136" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="47" t="inlineStr">
+      <c r="A137" s="54" t="inlineStr">
         <is>
           <t>3.56.60.056.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B137" s="47" t="inlineStr">
+      <c r="B137" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến điện áp TU 24kV 22000/√3/110/√3V-15VA CCX 0,5 epoxy chân không</t>
         </is>
       </c>
-      <c r="C137" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D137" s="48" t="n">
+      <c r="C137" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D137" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="E137" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F137" s="49" t="n">
+      <c r="E137" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F137" s="56" t="n">
         <v>46122</v>
       </c>
-      <c r="G137" s="48" t="inlineStr">
+      <c r="G137" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H137" s="48" t="n"/>
-      <c r="I137" s="47" t="inlineStr">
+      <c r="H137" s="55" t="n"/>
+      <c r="I137" s="54" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J137" s="50" t="n">
+      <c r="J137" s="57" t="n">
         <v>9</v>
       </c>
-      <c r="K137" s="50" t="n">
+      <c r="K137" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L137" s="50" t="n">
+      <c r="L137" s="57" t="n">
         <v>9</v>
       </c>
-      <c r="M137" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N137" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P137" s="52" t="inlineStr">
+      <c r="M137" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q137" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q137" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
@@ -10372,7 +10411,7 @@
       </c>
       <c r="Q147" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10541,7 @@
       </c>
       <c r="Q149" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
@@ -10567,7 +10606,7 @@
       </c>
       <c r="Q150" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10671,7 @@
       </c>
       <c r="Q151" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10736,7 @@
       </c>
       <c r="Q152" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
@@ -10762,7 +10801,7 @@
       </c>
       <c r="Q153" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
@@ -10827,7 +10866,7 @@
       </c>
       <c r="Q154" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
@@ -10892,7 +10931,7 @@
       </c>
       <c r="Q155" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
@@ -10957,7 +10996,7 @@
       </c>
       <c r="Q156" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11061,7 @@
       </c>
       <c r="Q157" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11126,7 @@
       </c>
       <c r="Q158" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
@@ -11217,7 +11256,7 @@
       </c>
       <c r="Q160" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
@@ -11282,7 +11321,7 @@
       </c>
       <c r="Q161" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
@@ -11347,7 +11386,7 @@
       </c>
       <c r="Q162" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
@@ -11412,7 +11451,7 @@
       </c>
       <c r="Q163" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
@@ -11477,7 +11516,7 @@
       </c>
       <c r="Q164" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
@@ -11672,7 +11711,7 @@
       </c>
       <c r="Q167" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
@@ -11737,7 +11776,7 @@
       </c>
       <c r="Q168" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
@@ -12262,67 +12301,67 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="47" t="inlineStr">
+      <c r="A177" s="54" t="inlineStr">
         <is>
           <t>3.56.60.121.000.00.AXX</t>
         </is>
       </c>
-      <c r="B177" s="47" t="inlineStr">
+      <c r="B177" s="54" t="inlineStr">
         <is>
           <t>Biến điện áp 22(15):V3/0,1:V3 kV - 15VA</t>
         </is>
       </c>
-      <c r="C177" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D177" s="48" t="n">
+      <c r="C177" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D177" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="E177" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F177" s="49" t="n">
+      <c r="E177" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F177" s="56" t="n">
         <v>46136</v>
       </c>
-      <c r="G177" s="48" t="inlineStr">
+      <c r="G177" s="55" t="inlineStr">
         <is>
           <t>01.VH4.11.0059</t>
         </is>
       </c>
-      <c r="H177" s="48" t="n"/>
-      <c r="I177" s="47" t="inlineStr">
+      <c r="H177" s="55" t="n"/>
+      <c r="I177" s="54" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập lại  TU, TI SCL T4-2026 03.VH4.41.0026</t>
         </is>
       </c>
-      <c r="J177" s="50" t="n">
+      <c r="J177" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="K177" s="50" t="n">
+      <c r="K177" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L177" s="50" t="n">
+      <c r="L177" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="M177" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N177" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O177" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P177" s="52" t="inlineStr">
+      <c r="M177" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q177" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q177" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
@@ -12457,197 +12496,197 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="47" t="inlineStr">
+      <c r="A180" s="54" t="inlineStr">
         <is>
           <t>3.53.65.148.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B180" s="47" t="inlineStr">
+      <c r="B180" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 50-100/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C180" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D180" s="48" t="n">
+      <c r="C180" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D180" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="E180" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F180" s="49" t="n">
+      <c r="E180" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F180" s="56" t="n">
         <v>46140</v>
       </c>
-      <c r="G180" s="48" t="inlineStr">
+      <c r="G180" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0038</t>
         </is>
       </c>
-      <c r="H180" s="48" t="n"/>
-      <c r="I180" s="47" t="inlineStr">
+      <c r="H180" s="55" t="n"/>
+      <c r="I180" s="54" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI, TU SCL</t>
         </is>
       </c>
-      <c r="J180" s="50" t="n">
+      <c r="J180" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="K180" s="50" t="n">
+      <c r="K180" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L180" s="50" t="n">
+      <c r="L180" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="M180" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N180" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O180" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P180" s="52" t="inlineStr">
+      <c r="M180" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q180" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q180" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="47" t="inlineStr">
+      <c r="A181" s="54" t="inlineStr">
         <is>
           <t>3.56.60.032.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B181" s="47" t="inlineStr">
+      <c r="B181" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến điện áp (TU 1P 12000/120V-15VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C181" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D181" s="48" t="n">
+      <c r="C181" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D181" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="E181" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F181" s="49" t="n">
+      <c r="E181" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F181" s="56" t="n">
         <v>46140</v>
       </c>
-      <c r="G181" s="48" t="inlineStr">
+      <c r="G181" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0038</t>
         </is>
       </c>
-      <c r="H181" s="48" t="n"/>
-      <c r="I181" s="47" t="inlineStr">
+      <c r="H181" s="55" t="n"/>
+      <c r="I181" s="54" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI, TU SCL</t>
         </is>
       </c>
-      <c r="J181" s="50" t="n">
+      <c r="J181" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="K181" s="50" t="n">
+      <c r="K181" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L181" s="50" t="n">
+      <c r="L181" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="M181" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N181" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O181" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P181" s="52" t="inlineStr">
+      <c r="M181" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q181" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q181" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="47" t="inlineStr">
+      <c r="A182" s="54" t="inlineStr">
         <is>
           <t>3.53.65.015.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B182" s="47" t="inlineStr">
+      <c r="B182" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 15-30/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C182" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D182" s="48" t="n">
+      <c r="C182" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D182" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="E182" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F182" s="49" t="n">
+      <c r="E182" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F182" s="56" t="n">
         <v>46140</v>
       </c>
-      <c r="G182" s="48" t="inlineStr">
+      <c r="G182" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0038</t>
         </is>
       </c>
-      <c r="H182" s="48" t="n"/>
-      <c r="I182" s="47" t="inlineStr">
+      <c r="H182" s="55" t="n"/>
+      <c r="I182" s="54" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI, TU SCL</t>
         </is>
       </c>
-      <c r="J182" s="50" t="n">
+      <c r="J182" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="K182" s="50" t="n">
+      <c r="K182" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L182" s="50" t="n">
+      <c r="L182" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="M182" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N182" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O182" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P182" s="52" t="inlineStr">
+      <c r="M182" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q182" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q182" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
@@ -12977,67 +13016,67 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="47" t="inlineStr">
+      <c r="A188" s="54" t="inlineStr">
         <is>
           <t>3.53.65.152.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B188" s="47" t="inlineStr">
+      <c r="B188" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24KV 150-300/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C188" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D188" s="48" t="n">
+      <c r="C188" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D188" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="E188" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F188" s="49" t="n">
+      <c r="E188" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F188" s="56" t="n">
         <v>46140</v>
       </c>
-      <c r="G188" s="48" t="inlineStr">
+      <c r="G188" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0038</t>
         </is>
       </c>
-      <c r="H188" s="48" t="n"/>
-      <c r="I188" s="47" t="inlineStr">
+      <c r="H188" s="55" t="n"/>
+      <c r="I188" s="54" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI, TU SCL</t>
         </is>
       </c>
-      <c r="J188" s="50" t="n">
+      <c r="J188" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="K188" s="50" t="n">
+      <c r="K188" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L188" s="50" t="n">
+      <c r="L188" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="M188" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N188" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O188" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P188" s="52" t="inlineStr">
+      <c r="M188" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q188" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q188" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
@@ -13822,67 +13861,67 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="47" t="inlineStr">
+      <c r="A201" s="54" t="inlineStr">
         <is>
           <t>3.56.60.032.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B201" s="47" t="inlineStr">
+      <c r="B201" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến điện áp (TU 1P 12000/120V-15VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C201" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D201" s="48" t="n">
+      <c r="C201" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D201" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="E201" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F201" s="49" t="n">
+      <c r="E201" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F201" s="56" t="n">
         <v>46140</v>
       </c>
-      <c r="G201" s="48" t="inlineStr">
+      <c r="G201" s="55" t="inlineStr">
         <is>
           <t>01.VH8.12.0037</t>
         </is>
       </c>
-      <c r="H201" s="48" t="n"/>
-      <c r="I201" s="47" t="inlineStr">
+      <c r="H201" s="55" t="n"/>
+      <c r="I201" s="54" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI, TU SCL</t>
         </is>
       </c>
-      <c r="J201" s="50" t="n">
+      <c r="J201" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="K201" s="50" t="n">
+      <c r="K201" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L201" s="50" t="n">
+      <c r="L201" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="M201" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N201" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O201" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P201" s="52" t="inlineStr">
+      <c r="M201" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q201" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q201" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
@@ -14147,67 +14186,67 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="47" t="inlineStr">
+      <c r="A206" s="54" t="inlineStr">
         <is>
           <t>3.53.65.015.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B206" s="47" t="inlineStr">
+      <c r="B206" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 15-30/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C206" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D206" s="48" t="n">
+      <c r="C206" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D206" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="E206" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F206" s="49" t="n">
+      <c r="E206" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F206" s="56" t="n">
         <v>46140</v>
       </c>
-      <c r="G206" s="48" t="inlineStr">
+      <c r="G206" s="55" t="inlineStr">
         <is>
           <t>01.VH8.12.0037</t>
         </is>
       </c>
-      <c r="H206" s="48" t="n"/>
-      <c r="I206" s="47" t="inlineStr">
+      <c r="H206" s="55" t="n"/>
+      <c r="I206" s="54" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI, TU SCL</t>
         </is>
       </c>
-      <c r="J206" s="50" t="n">
+      <c r="J206" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="K206" s="50" t="n">
+      <c r="K206" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L206" s="50" t="n">
+      <c r="L206" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="M206" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N206" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O206" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P206" s="52" t="inlineStr">
+      <c r="M206" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O206" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P206" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q206" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q206" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
@@ -16617,67 +16656,67 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="47" t="inlineStr">
+      <c r="A244" s="54" t="inlineStr">
         <is>
           <t>3.53.05.203.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B244" s="47" t="inlineStr">
+      <c r="B244" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 200/5A</t>
         </is>
       </c>
-      <c r="C244" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D244" s="48" t="n">
+      <c r="C244" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D244" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="E244" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F244" s="49" t="n">
+      <c r="E244" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F244" s="56" t="n">
         <v>46155</v>
       </c>
-      <c r="G244" s="48" t="inlineStr">
+      <c r="G244" s="55" t="inlineStr">
         <is>
           <t>01.VH8.12.0056</t>
         </is>
       </c>
-      <c r="H244" s="48" t="n"/>
-      <c r="I244" s="47" t="inlineStr">
+      <c r="H244" s="55" t="n"/>
+      <c r="I244" s="54" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J244" s="50" t="n">
+      <c r="J244" s="57" t="n">
         <v>7</v>
       </c>
-      <c r="K244" s="50" t="n">
+      <c r="K244" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L244" s="50" t="n">
+      <c r="L244" s="57" t="n">
         <v>7</v>
       </c>
-      <c r="M244" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N244" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O244" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P244" s="52" t="inlineStr">
+      <c r="M244" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N244" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O244" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P244" s="59" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q244" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q244" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
@@ -17852,132 +17891,132 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="47" t="inlineStr">
+      <c r="A263" s="54" t="inlineStr">
         <is>
           <t>3.53.05.150.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B263" s="47" t="inlineStr">
+      <c r="B263" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 150/5A 5VA CCX 0,5</t>
         </is>
       </c>
-      <c r="C263" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D263" s="48" t="n">
+      <c r="C263" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D263" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="E263" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F263" s="49" t="n">
+      <c r="E263" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F263" s="56" t="n">
         <v>46155</v>
       </c>
-      <c r="G263" s="48" t="inlineStr">
+      <c r="G263" s="55" t="inlineStr">
         <is>
           <t>01.VH8.12.0056</t>
         </is>
       </c>
-      <c r="H263" s="48" t="n"/>
-      <c r="I263" s="47" t="inlineStr">
+      <c r="H263" s="55" t="n"/>
+      <c r="I263" s="54" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J263" s="50" t="n">
+      <c r="J263" s="57" t="n">
         <v>25</v>
       </c>
-      <c r="K263" s="50" t="n">
+      <c r="K263" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L263" s="50" t="n">
+      <c r="L263" s="57" t="n">
         <v>25</v>
       </c>
-      <c r="M263" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N263" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O263" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P263" s="52" t="inlineStr">
+      <c r="M263" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N263" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O263" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P263" s="59" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q263" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q263" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="47" t="inlineStr">
+      <c r="A264" s="54" t="inlineStr">
         <is>
           <t>3.53.05.314.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B264" s="47" t="inlineStr">
+      <c r="B264" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 300/5A</t>
         </is>
       </c>
-      <c r="C264" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D264" s="48" t="n">
+      <c r="C264" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D264" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="E264" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F264" s="49" t="n">
+      <c r="E264" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F264" s="56" t="n">
         <v>46155</v>
       </c>
-      <c r="G264" s="48" t="inlineStr">
+      <c r="G264" s="55" t="inlineStr">
         <is>
           <t>01.VH8.12.0056</t>
         </is>
       </c>
-      <c r="H264" s="48" t="n"/>
-      <c r="I264" s="47" t="inlineStr">
+      <c r="H264" s="55" t="n"/>
+      <c r="I264" s="54" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J264" s="50" t="n">
+      <c r="J264" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="K264" s="50" t="n">
+      <c r="K264" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L264" s="50" t="n">
+      <c r="L264" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="M264" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N264" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O264" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P264" s="52" t="inlineStr">
+      <c r="M264" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N264" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O264" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P264" s="59" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q264" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q264" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
@@ -18437,587 +18476,587 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="47" t="inlineStr">
+      <c r="A272" s="54" t="inlineStr">
         <is>
           <t>3.53.05.105.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B272" s="47" t="inlineStr">
+      <c r="B272" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 100/5A</t>
         </is>
       </c>
-      <c r="C272" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D272" s="48" t="n">
+      <c r="C272" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D272" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="E272" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F272" s="49" t="n">
+      <c r="E272" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F272" s="56" t="n">
         <v>46155</v>
       </c>
-      <c r="G272" s="48" t="inlineStr">
+      <c r="G272" s="55" t="inlineStr">
         <is>
           <t>01.VH8.12.0056</t>
         </is>
       </c>
-      <c r="H272" s="48" t="n"/>
-      <c r="I272" s="47" t="inlineStr">
+      <c r="H272" s="55" t="n"/>
+      <c r="I272" s="54" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J272" s="50" t="n">
+      <c r="J272" s="57" t="n">
         <v>11</v>
       </c>
-      <c r="K272" s="50" t="n">
+      <c r="K272" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L272" s="50" t="n">
+      <c r="L272" s="57" t="n">
         <v>11</v>
       </c>
-      <c r="M272" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N272" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O272" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P272" s="52" t="inlineStr">
+      <c r="M272" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N272" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O272" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P272" s="59" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q272" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q272" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="47" t="inlineStr">
+      <c r="A273" s="54" t="inlineStr">
         <is>
           <t>3.53.05.150.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B273" s="47" t="inlineStr">
+      <c r="B273" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 150/5A 5VA CCX 0,5</t>
         </is>
       </c>
-      <c r="C273" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D273" s="48" t="n">
+      <c r="C273" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D273" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="E273" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F273" s="49" t="n">
+      <c r="E273" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F273" s="56" t="n">
         <v>46155</v>
       </c>
-      <c r="G273" s="48" t="inlineStr">
+      <c r="G273" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H273" s="48" t="n"/>
-      <c r="I273" s="47" t="inlineStr">
+      <c r="H273" s="55" t="n"/>
+      <c r="I273" s="54" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J273" s="50" t="n">
+      <c r="J273" s="57" t="n">
         <v>15</v>
       </c>
-      <c r="K273" s="50" t="n">
+      <c r="K273" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L273" s="50" t="n">
+      <c r="L273" s="57" t="n">
         <v>15</v>
       </c>
-      <c r="M273" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N273" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O273" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P273" s="52" t="inlineStr">
+      <c r="M273" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N273" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O273" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P273" s="59" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q273" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q273" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="47" t="inlineStr">
+      <c r="A274" s="54" t="inlineStr">
         <is>
           <t>3.53.05.320.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B274" s="47" t="inlineStr">
+      <c r="B274" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 800/5A</t>
         </is>
       </c>
-      <c r="C274" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D274" s="48" t="n">
+      <c r="C274" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D274" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="E274" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F274" s="49" t="n">
+      <c r="E274" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F274" s="56" t="n">
         <v>46155</v>
       </c>
-      <c r="G274" s="48" t="inlineStr">
+      <c r="G274" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H274" s="48" t="n"/>
-      <c r="I274" s="47" t="inlineStr">
+      <c r="H274" s="55" t="n"/>
+      <c r="I274" s="54" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J274" s="50" t="n">
+      <c r="J274" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="K274" s="50" t="n">
+      <c r="K274" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L274" s="50" t="n">
+      <c r="L274" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="M274" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N274" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O274" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P274" s="52" t="inlineStr">
+      <c r="M274" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N274" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O274" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P274" s="59" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q274" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q274" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="47" t="inlineStr">
+      <c r="A275" s="54" t="inlineStr">
         <is>
           <t>3.53.05.334.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B275" s="47" t="inlineStr">
+      <c r="B275" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 1000/5A-5VA-CCX 0,5</t>
         </is>
       </c>
-      <c r="C275" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D275" s="48" t="n">
+      <c r="C275" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D275" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="E275" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F275" s="49" t="n">
+      <c r="E275" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F275" s="56" t="n">
         <v>46155</v>
       </c>
-      <c r="G275" s="48" t="inlineStr">
+      <c r="G275" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H275" s="48" t="n"/>
-      <c r="I275" s="47" t="inlineStr">
+      <c r="H275" s="55" t="n"/>
+      <c r="I275" s="54" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J275" s="50" t="n">
+      <c r="J275" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="K275" s="50" t="n">
+      <c r="K275" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L275" s="50" t="n">
+      <c r="L275" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="M275" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N275" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O275" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P275" s="52" t="inlineStr">
+      <c r="M275" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N275" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O275" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P275" s="59" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q275" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q275" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="47" t="inlineStr">
+      <c r="A276" s="54" t="inlineStr">
         <is>
           <t>3.56.60.224.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B276" s="47" t="inlineStr">
+      <c r="B276" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến điện áp (TU) 24KV 22000/√3/100/√3V 15VA CCX0,5</t>
         </is>
       </c>
-      <c r="C276" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D276" s="48" t="n">
+      <c r="C276" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D276" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="E276" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F276" s="49" t="n">
+      <c r="E276" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F276" s="56" t="n">
         <v>46155</v>
       </c>
-      <c r="G276" s="48" t="inlineStr">
+      <c r="G276" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H276" s="48" t="n"/>
-      <c r="I276" s="47" t="inlineStr">
+      <c r="H276" s="55" t="n"/>
+      <c r="I276" s="54" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J276" s="50" t="n">
+      <c r="J276" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="K276" s="50" t="n">
+      <c r="K276" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L276" s="50" t="n">
+      <c r="L276" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="M276" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N276" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O276" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P276" s="52" t="inlineStr">
+      <c r="M276" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N276" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O276" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P276" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q276" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q276" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="47" t="inlineStr">
+      <c r="A277" s="54" t="inlineStr">
         <is>
           <t>3.53.05.264.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B277" s="47" t="inlineStr">
+      <c r="B277" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 250/5A</t>
         </is>
       </c>
-      <c r="C277" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D277" s="48" t="n">
+      <c r="C277" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D277" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="E277" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F277" s="49" t="n">
+      <c r="E277" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F277" s="56" t="n">
         <v>46155</v>
       </c>
-      <c r="G277" s="48" t="inlineStr">
+      <c r="G277" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H277" s="48" t="n"/>
-      <c r="I277" s="47" t="inlineStr">
+      <c r="H277" s="55" t="n"/>
+      <c r="I277" s="54" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J277" s="50" t="n">
+      <c r="J277" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="K277" s="50" t="n">
+      <c r="K277" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L277" s="50" t="n">
+      <c r="L277" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="M277" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N277" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O277" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P277" s="52" t="inlineStr">
+      <c r="M277" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N277" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O277" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P277" s="59" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q277" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q277" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="47" t="inlineStr">
+      <c r="A278" s="54" t="inlineStr">
         <is>
           <t>3.53.05.319.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B278" s="47" t="inlineStr">
+      <c r="B278" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 600/5A</t>
         </is>
       </c>
-      <c r="C278" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D278" s="48" t="n">
+      <c r="C278" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D278" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="E278" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F278" s="49" t="n">
+      <c r="E278" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F278" s="56" t="n">
         <v>46155</v>
       </c>
-      <c r="G278" s="48" t="inlineStr">
+      <c r="G278" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H278" s="48" t="n"/>
-      <c r="I278" s="47" t="inlineStr">
+      <c r="H278" s="55" t="n"/>
+      <c r="I278" s="54" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J278" s="50" t="n">
+      <c r="J278" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="K278" s="50" t="n">
+      <c r="K278" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L278" s="50" t="n">
+      <c r="L278" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="M278" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N278" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O278" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P278" s="52" t="inlineStr">
+      <c r="M278" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N278" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P278" s="59" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q278" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q278" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="47" t="inlineStr">
+      <c r="A279" s="54" t="inlineStr">
         <is>
           <t>3.53.05.330.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B279" s="47" t="inlineStr">
+      <c r="B279" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 400/5A-5VA-CCX 0,5</t>
         </is>
       </c>
-      <c r="C279" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D279" s="48" t="n">
+      <c r="C279" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D279" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="E279" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F279" s="49" t="n">
+      <c r="E279" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F279" s="56" t="n">
         <v>46155</v>
       </c>
-      <c r="G279" s="48" t="inlineStr">
+      <c r="G279" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H279" s="48" t="n"/>
-      <c r="I279" s="47" t="inlineStr">
+      <c r="H279" s="55" t="n"/>
+      <c r="I279" s="54" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J279" s="50" t="n">
+      <c r="J279" s="57" t="n">
         <v>17</v>
       </c>
-      <c r="K279" s="50" t="n">
+      <c r="K279" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L279" s="50" t="n">
+      <c r="L279" s="57" t="n">
         <v>17</v>
       </c>
-      <c r="M279" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N279" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O279" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P279" s="52" t="inlineStr">
+      <c r="M279" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N279" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P279" s="59" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q279" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q279" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="47" t="inlineStr">
+      <c r="A280" s="54" t="inlineStr">
         <is>
           <t>3.53.05.203.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B280" s="47" t="inlineStr">
+      <c r="B280" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 200/5A</t>
         </is>
       </c>
-      <c r="C280" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D280" s="48" t="n">
+      <c r="C280" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D280" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="E280" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F280" s="49" t="n">
+      <c r="E280" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F280" s="56" t="n">
         <v>46155</v>
       </c>
-      <c r="G280" s="48" t="inlineStr">
+      <c r="G280" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H280" s="48" t="n"/>
-      <c r="I280" s="47" t="inlineStr">
+      <c r="H280" s="55" t="n"/>
+      <c r="I280" s="54" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J280" s="50" t="n">
+      <c r="J280" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="K280" s="50" t="n">
+      <c r="K280" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L280" s="50" t="n">
+      <c r="L280" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="M280" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N280" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O280" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P280" s="52" t="inlineStr">
+      <c r="M280" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N280" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P280" s="59" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q280" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q280" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
@@ -19087,132 +19126,132 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="47" t="inlineStr">
+      <c r="A282" s="54" t="inlineStr">
         <is>
           <t>3.53.05.318.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B282" s="47" t="inlineStr">
+      <c r="B282" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 500/5A</t>
         </is>
       </c>
-      <c r="C282" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D282" s="48" t="n">
+      <c r="C282" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D282" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="E282" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F282" s="49" t="n">
+      <c r="E282" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F282" s="56" t="n">
         <v>46155</v>
       </c>
-      <c r="G282" s="48" t="inlineStr">
+      <c r="G282" s="55" t="inlineStr">
         <is>
           <t>01.VH8.12.0056</t>
         </is>
       </c>
-      <c r="H282" s="48" t="n"/>
-      <c r="I282" s="47" t="inlineStr">
+      <c r="H282" s="55" t="n"/>
+      <c r="I282" s="54" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J282" s="50" t="n">
+      <c r="J282" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="K282" s="50" t="n">
+      <c r="K282" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L282" s="50" t="n">
+      <c r="L282" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="M282" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N282" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O282" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P282" s="52" t="inlineStr">
+      <c r="M282" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N282" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P282" s="59" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q282" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q282" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="47" t="inlineStr">
+      <c r="A283" s="54" t="inlineStr">
         <is>
           <t>3.53.05.318.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B283" s="47" t="inlineStr">
+      <c r="B283" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 500/5A</t>
         </is>
       </c>
-      <c r="C283" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D283" s="48" t="n">
+      <c r="C283" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D283" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="E283" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F283" s="49" t="n">
+      <c r="E283" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F283" s="56" t="n">
         <v>46155</v>
       </c>
-      <c r="G283" s="48" t="inlineStr">
+      <c r="G283" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H283" s="48" t="n"/>
-      <c r="I283" s="47" t="inlineStr">
+      <c r="H283" s="55" t="n"/>
+      <c r="I283" s="54" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J283" s="50" t="n">
+      <c r="J283" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="K283" s="50" t="n">
+      <c r="K283" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L283" s="50" t="n">
+      <c r="L283" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="M283" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N283" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O283" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P283" s="52" t="inlineStr">
+      <c r="M283" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N283" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O283" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P283" s="59" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q283" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q283" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
@@ -19282,67 +19321,67 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="47" t="inlineStr">
+      <c r="A285" s="54" t="inlineStr">
         <is>
           <t>3.56.60.016.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B285" s="47" t="inlineStr">
+      <c r="B285" s="54" t="inlineStr">
         <is>
           <t>SPC - Biến điện áp TU 12000/120V</t>
         </is>
       </c>
-      <c r="C285" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D285" s="48" t="n">
+      <c r="C285" s="55" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D285" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="E285" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F285" s="49" t="n">
+      <c r="E285" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F285" s="56" t="n">
         <v>46157</v>
       </c>
-      <c r="G285" s="48" t="inlineStr">
+      <c r="G285" s="55" t="inlineStr">
         <is>
           <t>01.VH4.12.0045</t>
         </is>
       </c>
-      <c r="H285" s="48" t="n"/>
-      <c r="I285" s="47" t="inlineStr">
+      <c r="H285" s="55" t="n"/>
+      <c r="I285" s="54" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TU SCL T5-2026</t>
         </is>
       </c>
-      <c r="J285" s="50" t="n">
+      <c r="J285" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="K285" s="50" t="n">
+      <c r="K285" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="L285" s="50" t="n">
+      <c r="L285" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="M285" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N285" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O285" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P285" s="52" t="inlineStr">
+      <c r="M285" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N285" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O285" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P285" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q285" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q285" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
@@ -19927,7 +19966,7 @@
       </c>
       <c r="Q294" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
@@ -20062,67 +20101,67 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="47" t="inlineStr">
+      <c r="A297" s="54" t="inlineStr">
         <is>
           <t>3.30.92.025.VIE.00.000</t>
         </is>
       </c>
-      <c r="B297" s="47" t="inlineStr">
+      <c r="B297" s="54" t="inlineStr">
         <is>
           <t>SPC - Dây chì (FUSE LINK) 25A</t>
         </is>
       </c>
-      <c r="C297" s="48" t="inlineStr">
+      <c r="C297" s="55" t="inlineStr">
         <is>
           <t>Sợi</t>
         </is>
       </c>
-      <c r="D297" s="48" t="n">
+      <c r="D297" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="E297" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F297" s="49" t="n">
+      <c r="E297" s="55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F297" s="56" t="n">
         <v>46167</v>
       </c>
-      <c r="G297" s="48" t="inlineStr">
+      <c r="G297" s="55" t="inlineStr">
         <is>
           <t>01.VH6.11.0002</t>
         </is>
       </c>
-      <c r="H297" s="48" t="n"/>
-      <c r="I297" s="47" t="inlineStr">
+      <c r="H297" s="55" t="n"/>
+      <c r="I297" s="54" t="inlineStr">
         <is>
           <t>VTAD2606002-Nhập Vtư trả lại kho VHJ (PX 02.VH6.41.0006/24.04.26; 07.VHJ.56.0001/24.04.26)</t>
         </is>
       </c>
-      <c r="J297" s="50" t="n">
+      <c r="J297" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="K297" s="50" t="n">
+      <c r="K297" s="57" t="n">
         <v>46000</v>
       </c>
-      <c r="L297" s="50" t="n">
+      <c r="L297" s="57" t="n">
         <v>138000</v>
       </c>
-      <c r="M297" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N297" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O297" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P297" s="52" t="inlineStr">
+      <c r="M297" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N297" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O297" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P297" s="59" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q297" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="Q297" s="60" t="inlineStr">
+        <is>
+          <t>Thu hồi VTTB</t>
         </is>
       </c>
     </row>
@@ -20837,7 +20876,7 @@
       </c>
       <c r="Q308" s="53" t="inlineStr">
         <is>
-          <t>Thu hồi/Nhập kho</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
     </row>
